--- a/Luckyday/pet/petskill_v22.xlsx
+++ b/Luckyday/pet/petskill_v22.xlsx
@@ -1191,17 +1191,17 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>두두에게 방패 1개와 최대 체력의 15%만큼 보호막을 부여합니다.</t>
+          <t>두두에게 최대 체력의 15%만큼 보호막을 부여합니다.</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
+          <t>액티브 스킬 사용 시 보호막의 양이 5% 추가됩니다. (총 20%)</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
           <t>방패 소모 시 쿨타임이 1 감소하고, 적에게 저체온 1스택을 부여합니다.</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>액티브 스킬 사용 시 보호막의 양이 5% 추가됩니다. (총 20%)</t>
         </is>
       </c>
       <c r="K14" s="14" t="n"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
-          <t>두두에게 방패 2개를 부여합니다.</t>
+          <t>두두에게 최대 체력의 15%만큼 보호막과 방패 1개를 부여합니다.</t>
         </is>
       </c>
       <c r="I25" s="16" t="inlineStr">
@@ -2058,32 +2058,32 @@
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>거미줄의 군주</t>
+          <t>가시방패의 군주</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>2턴간 거미줄 진을 전개합니다. 적이 공격할 때마다 방패 1개가 자동 생성되고, 적에게 어지러움 1스택을 부여합니다.</t>
+          <t>두두에게 최대 체력의 20%만큼 보호막과 방패 3개를 부여합니다.</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>방패 소모 시 쿨타임이 1 감소하고, 적에게 받는 피해 15% 증가 디버프를 1턴간 걸어줍니다.</t>
+          <t>액티브 스킬 사용 시 보호막의 양이 10% 추가됩니다. (총 30%)</t>
         </is>
       </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>거미줄 진 효과 중 방패가 3개 이상 축적되면 전부 소모하고, 적에게 저체온 3스택을 부여합니다.</t>
+          <t>방패 소모 시 쿨타임이 1 감소합니다.</t>
         </is>
       </c>
       <c r="K30" s="19" t="inlineStr">
         <is>
-          <t>액티브 스킬 사용 시 두두에게 최대 체력의 15%만큼 보호막을 부여합니다.</t>
+          <t>방패 소모 시 적에게 어지러움 1스택을 부여합니다.</t>
         </is>
       </c>
       <c r="L30" s="19" t="inlineStr">
         <is>
-          <t>매 3라운드 시작 시 적에게 어지러움 1스택을 자동으로 부여합니다.</t>
+          <t>매 3라운드 시작 시 방패를 2개 생성해줍니다.</t>
         </is>
       </c>
       <c r="M30" s="20" t="inlineStr">
